--- a/Material/2. Interviews/1. Qualitative Interview/Attribute Definition.xlsx
+++ b/Material/2. Interviews/1. Qualitative Interview/Attribute Definition.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Documents\GitHub\DSE_thesis\Material\Interviews\1. Qualitative Interview\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a2d5831973e105bc/Documents/GitHub/DSE_thesis/Material/2. Interviews/1. Qualitative Interview/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C15FE2-8924-40D9-B65A-360832DA0470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{B2C15FE2-8924-40D9-B65A-360832DA0470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C16C3A67-800C-4AB3-B37C-FEA14BA54BE2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1010D4BD-99A2-4997-AD21-2857331DB82F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1010D4BD-99A2-4997-AD21-2857331DB82F}"/>
   </bookViews>
   <sheets>
     <sheet name="Attribute_Frequency_Table" sheetId="2" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
   <si>
     <t>Attribute</t>
   </si>
@@ -785,48 +785,48 @@
     </xf>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Bueno" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Cálculo" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Celda de comprobación" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Celda vinculada" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Encabezado 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Encabezado 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Énfasis1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Énfasis2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Énfasis3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Énfasis4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Énfasis5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Énfasis6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Incorrecto" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Notas" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Salida" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Texto de advertencia" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Texto explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Título" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Título 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -863,7 +863,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1180,7 +1180,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{753A4EC4-A069-4538-AB5A-AA8E0DF18E9E}">
   <dimension ref="A1:D45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -1363,7 +1363,9 @@
         <f>+VLOOKUP($A11,Attributes_by_Interview!$A:$C,3,0)</f>
         <v>6</v>
       </c>
-      <c r="D11" s="6"/>
+      <c r="D11" s="6" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
@@ -1888,7 +1890,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374489E4-D186-42D3-A4E8-3A21A6E3345B}">
   <dimension ref="A1:M45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" style="1" bestFit="1" customWidth="1"/>

--- a/Material/2. Interviews/1. Qualitative Interview/Attribute Definition.xlsx
+++ b/Material/2. Interviews/1. Qualitative Interview/Attribute Definition.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a2d5831973e105bc/Documents/GitHub/DSE_thesis/Material/2. Interviews/1. Qualitative Interview/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Documents\GitHub\DSE_thesis\Material\2. Interviews\1. Qualitative Interview\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{B2C15FE2-8924-40D9-B65A-360832DA0470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C16C3A67-800C-4AB3-B37C-FEA14BA54BE2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C39A59D0-A425-4E45-833E-8649DEE43C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1010D4BD-99A2-4997-AD21-2857331DB82F}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
   <si>
     <t>Attribute</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>*</t>
+  </si>
+  <si>
+    <t>Ease to reach destination</t>
   </si>
 </sst>
 </file>
@@ -1179,7 +1182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{753A4EC4-A069-4538-AB5A-AA8E0DF18E9E}">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -1188,7 +1191,7 @@
     <col min="4" max="4" width="13.6640625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>56</v>
       </c>
@@ -1202,7 +1205,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1218,7 +1221,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <f>+A2+1</f>
         <v>2</v>
@@ -1235,7 +1238,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <f t="shared" ref="A4:A45" si="0">+A3+1</f>
         <v>3</v>
@@ -1252,7 +1255,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1269,7 +1272,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1286,7 +1289,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1302,8 +1305,11 @@
       <c r="D7" s="6" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1318,7 +1324,7 @@
       </c>
       <c r="D8" s="6"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1333,7 +1339,7 @@
       </c>
       <c r="D9" s="6"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1350,7 +1356,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1367,7 +1373,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1382,7 +1388,7 @@
       </c>
       <c r="D12" s="6"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1397,7 +1403,7 @@
       </c>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1412,7 +1418,7 @@
       </c>
       <c r="D14" s="6"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1427,7 +1433,7 @@
       </c>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1879,7 +1885,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"*"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Material/2. Interviews/1. Qualitative Interview/Attribute Definition.xlsx
+++ b/Material/2. Interviews/1. Qualitative Interview/Attribute Definition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Documents\GitHub\DSE_thesis\Material\2. Interviews\1. Qualitative Interview\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C39A59D0-A425-4E45-833E-8649DEE43C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9F2A9D-3D84-45FA-9103-25A4B9148A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1010D4BD-99A2-4997-AD21-2857331DB82F}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="71">
   <si>
     <t>Attribute</t>
   </si>
@@ -231,6 +231,36 @@
   </si>
   <si>
     <t>Ease to reach destination</t>
+  </si>
+  <si>
+    <t>New attributes after visit:</t>
+  </si>
+  <si>
+    <t>Accommodation type</t>
+  </si>
+  <si>
+    <t>Online recommendations</t>
+  </si>
+  <si>
+    <t>Local cuisine</t>
+  </si>
+  <si>
+    <t>Cost to reach destination</t>
+  </si>
+  <si>
+    <t>Proximity to other touristic destinations</t>
+  </si>
+  <si>
+    <t>Availability of tourist attractions at the destination</t>
+  </si>
+  <si>
+    <t>Proximity to the beach</t>
+  </si>
+  <si>
+    <t>Historical buildings</t>
+  </si>
+  <si>
+    <t>Local events</t>
   </si>
 </sst>
 </file>
@@ -381,7 +411,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -564,6 +594,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -765,7 +801,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -786,6 +822,10 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1182,16 +1222,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{753A4EC4-A069-4538-AB5A-AA8E0DF18E9E}">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>56</v>
       </c>
@@ -1205,7 +1247,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1221,7 +1263,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <f>+A2+1</f>
         <v>2</v>
@@ -1237,8 +1279,14 @@
       <c r="D3" s="6" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <f t="shared" ref="A4:A45" si="0">+A3+1</f>
         <v>3</v>
@@ -1254,8 +1302,14 @@
       <c r="D4" s="6" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1271,8 +1325,17 @@
       <c r="D5" s="6" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I5" t="s">
+        <v>63</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1288,8 +1351,14 @@
       <c r="D6" s="6" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I6" t="s">
+        <v>66</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1308,8 +1377,17 @@
       <c r="E7" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I7" t="s">
+        <v>64</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="N7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1323,8 +1401,14 @@
         <v>6</v>
       </c>
       <c r="D8" s="6"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I8" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1338,8 +1422,14 @@
         <v>6</v>
       </c>
       <c r="D9" s="6"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I9" t="s">
+        <v>65</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1355,8 +1445,14 @@
       <c r="D10" s="6" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I10" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1372,8 +1468,14 @@
       <c r="D11" s="6" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I11" t="s">
+        <v>68</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1387,8 +1489,11 @@
         <v>5</v>
       </c>
       <c r="D12" s="6"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1402,8 +1507,11 @@
         <v>5</v>
       </c>
       <c r="D13" s="6"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1418,7 +1526,7 @@
       </c>
       <c r="D14" s="6"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1433,7 +1541,7 @@
       </c>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>15</v>

--- a/Material/2. Interviews/1. Qualitative Interview/Attribute Definition.xlsx
+++ b/Material/2. Interviews/1. Qualitative Interview/Attribute Definition.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Documents\GitHub\DSE_thesis\Material\2. Interviews\1. Qualitative Interview\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9F2A9D-3D84-45FA-9103-25A4B9148A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB7826D-EB9A-4C75-9FB0-A732887EAA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1010D4BD-99A2-4997-AD21-2857331DB82F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Attribute_Frequency_Table" sheetId="2" r:id="rId1"/>
-    <sheet name="Attributes_by_Interview" sheetId="3" r:id="rId2"/>
+    <sheet name="Improvement" sheetId="4" r:id="rId1"/>
+    <sheet name="Attribute_Frequency_Table" sheetId="2" r:id="rId2"/>
+    <sheet name="Attributes_by_Interview" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Attributes_by_Interview!$B$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Attributes_by_Interview!$B$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="115">
   <si>
     <t>Attribute</t>
   </si>
@@ -261,6 +262,138 @@
   </si>
   <si>
     <t>Local events</t>
+  </si>
+  <si>
+    <t>Too generic</t>
+  </si>
+  <si>
+    <t>Process attribute</t>
+  </si>
+  <si>
+    <t>Original Attributes</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>New Attribute</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Could be included in point 6</t>
+  </si>
+  <si>
+    <t>Replaced by Ease to reach the destination</t>
+  </si>
+  <si>
+    <t>Authenticity/Culture</t>
+  </si>
+  <si>
+    <t>Already have an accommodation attribute (point 1)</t>
+  </si>
+  <si>
+    <t>Natural spots</t>
+  </si>
+  <si>
+    <t>Covered by point 3</t>
+  </si>
+  <si>
+    <t>Covered by point 4</t>
+  </si>
+  <si>
+    <t>Covered by point 4, 9 and 10</t>
+  </si>
+  <si>
+    <t>Too general</t>
+  </si>
+  <si>
+    <t>Also could be more spcific to segment among people who access places by transport or by foot</t>
+  </si>
+  <si>
+    <t>Also could be more specific to segment better between those who prefer going by car than public transport</t>
+  </si>
+  <si>
+    <t>Could be added, but making sure that it does not is redundant with other attributes</t>
+  </si>
+  <si>
+    <t>Is too generic and may refer to attraction information, accommodation, and so on.</t>
+  </si>
+  <si>
+    <t>Proximity to natural areas (Proximidad a áreas naturales)</t>
+  </si>
+  <si>
+    <t>This could be stational, and also when checking interviews, in general this was mentioned when asking about Ascoli's Quintana event. Better to foucs in historcial buildings and local cuisine</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Distinctive local cuisine (Gastronomía local distintiva)</t>
+  </si>
+  <si>
+    <t>This could be stational, so is better to have a more general meaning, but keeping the idea of having near beaches, mountains, and so on.</t>
+  </si>
+  <si>
+    <t>This was mentioned a lot, mainly when referring to Italy in general, so it would be good to keep it. A good idea would be to be more specific, without leaving space to overthinking the option.</t>
+  </si>
+  <si>
+    <t>Attribute also mentioned a lot, so is good to keep it, so it will be reformulated to make sure that we are talking of specific gastronomy of the destination.</t>
+  </si>
+  <si>
+    <t>Main Target:</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Male and female</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>18 onwards</t>
+  </si>
+  <si>
+    <t>When travelling</t>
+  </si>
+  <si>
+    <t>Independent. They make their own decisions about the destination and organize it themselves. This may exclude young people who depend on their parents.</t>
+  </si>
+  <si>
+    <t>Nationality</t>
+  </si>
+  <si>
+    <t>Ideally foreigners (Ascoli needs more international tourists)</t>
+  </si>
+  <si>
+    <t>Additional characteristic:</t>
+  </si>
+  <si>
+    <t>They never visited Ascoli Piceno</t>
+  </si>
+  <si>
+    <t>The idea is to filtrate the respondents in some short questions at the beginning</t>
+  </si>
+  <si>
+    <t>Low Tourist Density (Baja densidad de turistas)</t>
+  </si>
+  <si>
+    <t>Ease of reaching the city by public transport (Facilidad para llegar a la ciudad en transporte público)</t>
+  </si>
+  <si>
+    <t>Heritage ambience of the historic center (Ambiente patrimonial del centro histórico)</t>
+  </si>
+  <si>
+    <t>Density of touristic attractions within walking distance (Densidad de atractivos turisticos a distancia caminable)</t>
+  </si>
+  <si>
+    <t>Accommodation services (Servicios del alojamiento)</t>
+  </si>
+  <si>
+    <t>Availability of centrally located accommodation (Disponibilidad de alojamiento en el centro)</t>
   </si>
 </sst>
 </file>
@@ -411,7 +544,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -600,6 +733,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -801,7 +940,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -826,6 +965,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1221,6 +1387,278 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35B2167B-80CA-4E4B-99D3-44B58628E678}">
+  <dimension ref="B1:E39"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="4.88671875" style="13" customWidth="1"/>
+    <col min="2" max="2" width="44.6640625" style="13" customWidth="1"/>
+    <col min="3" max="3" width="67.77734375" style="14" customWidth="1"/>
+    <col min="4" max="4" width="69.44140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="15">
+        <f>+SUM(E2:E1048576)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B5" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B6" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B9" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B10" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E10" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B11" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D12" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D13" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E13" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B18" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B20" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B21" s="16"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B22" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="18"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B23" s="16"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="16"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B25" s="16"/>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B26" s="16"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B27" s="16"/>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B28" s="16"/>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B29" s="16"/>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B30" s="16"/>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B31" s="16"/>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B32" s="16"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="16"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="16"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="16"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B36" s="16"/>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B37" s="16"/>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B38" s="16"/>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B39" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{753A4EC4-A069-4538-AB5A-AA8E0DF18E9E}">
   <dimension ref="A1:N45"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1279,6 +1717,9 @@
       <c r="D3" s="6" t="s">
         <v>59</v>
       </c>
+      <c r="E3" t="s">
+        <v>72</v>
+      </c>
       <c r="H3" t="s">
         <v>61</v>
       </c>
@@ -1325,6 +1766,9 @@
       <c r="D5" s="6" t="s">
         <v>59</v>
       </c>
+      <c r="E5" t="s">
+        <v>79</v>
+      </c>
       <c r="I5" t="s">
         <v>63</v>
       </c>
@@ -1375,7 +1819,7 @@
         <v>59</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="I7" t="s">
         <v>64</v>
@@ -1401,6 +1845,9 @@
         <v>6</v>
       </c>
       <c r="D8" s="6"/>
+      <c r="E8" t="s">
+        <v>80</v>
+      </c>
       <c r="I8" t="s">
         <v>67</v>
       </c>
@@ -1422,6 +1869,9 @@
         <v>6</v>
       </c>
       <c r="D9" s="6"/>
+      <c r="E9" t="s">
+        <v>77</v>
+      </c>
       <c r="I9" t="s">
         <v>65</v>
       </c>
@@ -1445,6 +1895,9 @@
       <c r="D10" s="6" t="s">
         <v>59</v>
       </c>
+      <c r="E10" t="s">
+        <v>79</v>
+      </c>
       <c r="I10" t="s">
         <v>60</v>
       </c>
@@ -1468,6 +1921,9 @@
       <c r="D11" s="6" t="s">
         <v>59</v>
       </c>
+      <c r="E11" t="s">
+        <v>79</v>
+      </c>
       <c r="I11" t="s">
         <v>68</v>
       </c>
@@ -1489,6 +1945,9 @@
         <v>5</v>
       </c>
       <c r="D12" s="6"/>
+      <c r="E12" t="s">
+        <v>80</v>
+      </c>
       <c r="I12" t="s">
         <v>69</v>
       </c>
@@ -1507,6 +1966,9 @@
         <v>5</v>
       </c>
       <c r="D13" s="6"/>
+      <c r="E13" t="s">
+        <v>77</v>
+      </c>
       <c r="I13" t="s">
         <v>70</v>
       </c>
@@ -1525,6 +1987,9 @@
         <v>5</v>
       </c>
       <c r="D14" s="6"/>
+      <c r="E14" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
@@ -1540,6 +2005,9 @@
         <v>5</v>
       </c>
       <c r="D15" s="6"/>
+      <c r="E15" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
@@ -1555,13 +2023,16 @@
         <v>5</v>
       </c>
       <c r="D16" s="6"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="str">
+      <c r="B17" s="10" t="str">
         <f>+VLOOKUP($A17,Attributes_by_Interview!$A:$C,2,0)</f>
         <v>accommodation location</v>
       </c>
@@ -1570,8 +2041,11 @@
         <v>4</v>
       </c>
       <c r="D17" s="6"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1585,8 +2059,11 @@
         <v>4</v>
       </c>
       <c r="D18" s="6"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1600,8 +2077,11 @@
         <v>4</v>
       </c>
       <c r="D19" s="6"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1615,8 +2095,11 @@
         <v>4</v>
       </c>
       <c r="D20" s="6"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1630,8 +2113,11 @@
         <v>3</v>
       </c>
       <c r="D21" s="6"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1645,8 +2131,11 @@
         <v>3</v>
       </c>
       <c r="D22" s="6"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1660,13 +2149,16 @@
         <v>3</v>
       </c>
       <c r="D23" s="6"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="str">
+      <c r="B24" s="10" t="str">
         <f>+VLOOKUP($A24,Attributes_by_Interview!$A:$C,2,0)</f>
         <v>overcrowded</v>
       </c>
@@ -1675,8 +2167,11 @@
         <v>3</v>
       </c>
       <c r="D24" s="6"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E24" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -1691,7 +2186,7 @@
       </c>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -1706,7 +2201,7 @@
       </c>
       <c r="D26" s="6"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -1721,7 +2216,7 @@
       </c>
       <c r="D27" s="6"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -1736,7 +2231,7 @@
       </c>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -1751,7 +2246,7 @@
       </c>
       <c r="D29" s="6"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -1766,7 +2261,7 @@
       </c>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1781,7 +2276,7 @@
       </c>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2001,7 +2496,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374489E4-D186-42D3-A4E8-3A21A6E3345B}">
   <dimension ref="A1:M45"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
